--- a/Raw Data/two forces (15 trials)(tapered and cylindrical)/Validation(Ellipse2.00and1.25)(3tendon).xlsx
+++ b/Raw Data/two forces (15 trials)(tapered and cylindrical)/Validation(Ellipse2.00and1.25)(3tendon).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces (15 trials)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2961" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24EAA8B6-3B26-4D23-8107-E8D14DE318E8}"/>
+  <xr:revisionPtr revIDLastSave="2962" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{118F7A74-8D0D-4128-867C-7B7762A4B48B}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" firstSheet="1" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (double)" sheetId="12" r:id="rId1"/>
@@ -1587,27 +1587,27 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="V11" s="14">
-        <f>AVERAGE(V3:V10)</f>
+        <f t="shared" ref="V11:AA11" si="7">AVERAGE(V3:V10)</f>
         <v>-0.1943967459374108</v>
       </c>
       <c r="W11" s="14">
-        <f>AVERAGE(W3:W10)</f>
+        <f t="shared" si="7"/>
         <v>0.16195741109549985</v>
       </c>
       <c r="X11" s="14">
-        <f>AVERAGE(X3:X10)</f>
+        <f t="shared" si="7"/>
         <v>-0.1803508261218669</v>
       </c>
       <c r="Y11" s="14">
-        <f>AVERAGE(Y3:Y10)</f>
+        <f t="shared" si="7"/>
         <v>-0.27667640242725616</v>
       </c>
       <c r="Z11" s="14">
-        <f>AVERAGE(Z3:Z10)</f>
+        <f t="shared" si="7"/>
         <v>-0.58748469501733802</v>
       </c>
       <c r="AA11" s="14">
-        <f>AVERAGE(AA3:AA10)</f>
+        <f t="shared" si="7"/>
         <v>-0.13032413611654187</v>
       </c>
     </row>
@@ -1903,39 +1903,39 @@
         <v>1.1683698134950406E-2</v>
       </c>
       <c r="W3" s="5">
-        <f>P3-A3</f>
+        <f t="shared" ref="W3:AB10" si="0">P3-A3</f>
         <v>0.29999999999997773</v>
       </c>
       <c r="X3" s="5">
-        <f>Q3-B3</f>
+        <f t="shared" si="0"/>
         <v>-3.6884168274216811E-2</v>
       </c>
       <c r="Y3" s="5">
-        <f>R3-C3</f>
+        <f t="shared" si="0"/>
         <v>0.19746315054845009</v>
       </c>
       <c r="Z3" s="5">
-        <f>S3-D3</f>
+        <f t="shared" si="0"/>
         <v>-0.33341799174419812</v>
       </c>
       <c r="AA3" s="5">
-        <f>T3-E3</f>
+        <f t="shared" si="0"/>
         <v>-3.9999999999976096E-2</v>
       </c>
       <c r="AB3" s="5">
-        <f>U3-F3</f>
+        <f t="shared" si="0"/>
         <v>1.0752044931036768</v>
       </c>
       <c r="AC3" s="9">
-        <f t="shared" ref="AC3:AC10" si="0">AVERAGE(ABS(W3),ABS(Z3))</f>
+        <f t="shared" ref="AC3:AC10" si="1">AVERAGE(ABS(W3),ABS(Z3))</f>
         <v>0.3167089958720879</v>
       </c>
       <c r="AD3" s="9">
-        <f t="shared" ref="AD3:AD10" si="1">AVERAGE(ABS(X3),ABS(AA3))</f>
+        <f t="shared" ref="AD3:AD10" si="2">AVERAGE(ABS(X3),ABS(AA3))</f>
         <v>3.8442084137096454E-2</v>
       </c>
       <c r="AE3" s="9">
-        <f t="shared" ref="AE3:AE10" si="2">AVERAGE(ABS(Y3),ABS(AB3))</f>
+        <f t="shared" ref="AE3:AE10" si="3">AVERAGE(ABS(Y3),ABS(AB3))</f>
         <v>0.63633382182606346</v>
       </c>
       <c r="AF3" s="1" t="s">
@@ -2040,39 +2040,39 @@
         <v>1.036710516471954E-2</v>
       </c>
       <c r="W4" s="5">
-        <f>P4-A4</f>
+        <f t="shared" si="0"/>
         <v>-3.2975691673538865E-2</v>
       </c>
       <c r="X4" s="5">
-        <f>Q4-B4</f>
+        <f t="shared" si="0"/>
         <v>6.1351713346638997E-2</v>
       </c>
       <c r="Y4" s="5">
-        <f>R4-C4</f>
+        <f t="shared" si="0"/>
         <v>-1.2241624757141423</v>
       </c>
       <c r="Z4" s="5">
-        <f>S4-D4</f>
+        <f t="shared" si="0"/>
         <v>0.69999999954503012</v>
       </c>
       <c r="AA4" s="5">
-        <f>T4-E4</f>
+        <f t="shared" si="0"/>
         <v>8.230488043600212E-2</v>
       </c>
       <c r="AB4" s="5">
-        <f>U4-F4</f>
+        <f t="shared" si="0"/>
         <v>-0.44113134793381237</v>
       </c>
       <c r="AC4" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.36648784560928449</v>
       </c>
       <c r="AD4" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.1828296891320559E-2</v>
       </c>
       <c r="AE4" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.83264691182397732</v>
       </c>
       <c r="AF4" s="8" cm="1">
@@ -2183,39 +2183,39 @@
         <v>1.9737605556386574E-2</v>
       </c>
       <c r="W5" s="5">
-        <f>P5-A5</f>
+        <f t="shared" si="0"/>
         <v>0.19999999999997775</v>
       </c>
       <c r="X5" s="5">
-        <f>Q5-B5</f>
+        <f t="shared" si="0"/>
         <v>-8.6469819748300619E-3</v>
       </c>
       <c r="Y5" s="5">
-        <f>R5-C5</f>
+        <f t="shared" si="0"/>
         <v>0.13380765318501497</v>
       </c>
       <c r="Z5" s="5">
-        <f>S5-D5</f>
+        <f t="shared" si="0"/>
         <v>-4.4668854076280518E-2</v>
       </c>
       <c r="AA5" s="5">
-        <f>T5-E5</f>
+        <f t="shared" si="0"/>
         <v>-3.9999999999971364E-2</v>
       </c>
       <c r="AB5" s="5">
-        <f>U5-F5</f>
+        <f t="shared" si="0"/>
         <v>0.95428180806862217</v>
       </c>
       <c r="AC5" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12233442703812913</v>
       </c>
       <c r="AD5" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4323490987400713E-2</v>
       </c>
       <c r="AE5" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.54404473062681857</v>
       </c>
       <c r="AF5" s="24" t="s">
@@ -2310,39 +2310,39 @@
         <v>1.619745021370154E-3</v>
       </c>
       <c r="W6" s="5">
-        <f>P6-A6</f>
+        <f t="shared" si="0"/>
         <v>-0.10969435966814678</v>
       </c>
       <c r="X6" s="5">
-        <f>Q6-B6</f>
+        <f t="shared" si="0"/>
         <v>1.987920042442462E-2</v>
       </c>
       <c r="Y6" s="5">
-        <f>R6-C6</f>
+        <f t="shared" si="0"/>
         <v>-0.69193032994202719</v>
       </c>
       <c r="Z6" s="5">
-        <f>S6-D6</f>
+        <f t="shared" si="0"/>
         <v>0.15450803254305079</v>
       </c>
       <c r="AA6" s="5">
-        <f>T6-E6</f>
+        <f t="shared" si="0"/>
         <v>5.0565680530742417E-2</v>
       </c>
       <c r="AB6" s="5">
-        <f>U6-F6</f>
+        <f t="shared" si="0"/>
         <v>0.10693528204722069</v>
       </c>
       <c r="AC6" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13210119610559878</v>
       </c>
       <c r="AD6" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.5222440477583522E-2</v>
       </c>
       <c r="AE6" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.39943280599462394</v>
       </c>
       <c r="AF6" s="7" t="s">
@@ -2441,39 +2441,39 @@
         <v>2.7827099281207626E-4</v>
       </c>
       <c r="W7" s="5">
-        <f>P7-A7</f>
+        <f t="shared" si="0"/>
         <v>-0.12899116918824738</v>
       </c>
       <c r="X7" s="5">
-        <f>Q7-B7</f>
+        <f t="shared" si="0"/>
         <v>-4.0495384823202585E-14</v>
       </c>
       <c r="Y7" s="5">
-        <f>R7-C7</f>
+        <f t="shared" si="0"/>
         <v>-0.56656648462432413</v>
       </c>
       <c r="Z7" s="5">
-        <f>S7-D7</f>
+        <f t="shared" si="0"/>
         <v>0.22618934429340343</v>
       </c>
       <c r="AA7" s="5">
-        <f>T7-E7</f>
+        <f t="shared" si="0"/>
         <v>4.5998425103691835E-2</v>
       </c>
       <c r="AB7" s="5">
-        <f>U7-F7</f>
+        <f t="shared" si="0"/>
         <v>4.8547258275863925E-2</v>
       </c>
       <c r="AC7" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.1775902567408254</v>
       </c>
       <c r="AD7" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2999212551866165E-2</v>
       </c>
       <c r="AE7" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.30755687145009403</v>
       </c>
       <c r="AF7" s="11">
@@ -2575,39 +2575,39 @@
         <v>2.9143270943843805E-3</v>
       </c>
       <c r="W8" s="5">
-        <f>P8-A8</f>
+        <f t="shared" si="0"/>
         <v>0.5999973012459473</v>
       </c>
       <c r="X8" s="5">
-        <f>Q8-B8</f>
+        <f t="shared" si="0"/>
         <v>-6.371192435427224E-2</v>
       </c>
       <c r="Y8" s="5">
-        <f>R8-C8</f>
+        <f t="shared" si="0"/>
         <v>-2.267619363992468E-2</v>
       </c>
       <c r="Z8" s="5">
-        <f>S8-D8</f>
+        <f t="shared" si="0"/>
         <v>-5.2759771515438925E-2</v>
       </c>
       <c r="AA8" s="5">
-        <f>T8-E8</f>
+        <f t="shared" si="0"/>
         <v>9.7970405538573453E-3</v>
       </c>
       <c r="AB8" s="5">
-        <f>U8-F8</f>
+        <f t="shared" si="0"/>
         <v>-1.415139203332163</v>
       </c>
       <c r="AC8" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.32637853638069314</v>
       </c>
       <c r="AD8" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.6754482454064791E-2</v>
       </c>
       <c r="AE8" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.71890769848604386</v>
       </c>
     </row>
@@ -2694,39 +2694,39 @@
         <v>117.30863766147816</v>
       </c>
       <c r="W9" s="5">
-        <f>P9-A9</f>
+        <f t="shared" si="0"/>
         <v>0.28865521952038442</v>
       </c>
       <c r="X9" s="5">
-        <f>Q9-B9</f>
+        <f t="shared" si="0"/>
         <v>7.9947496212086078E-2</v>
       </c>
       <c r="Y9" s="5">
-        <f>R9-C9</f>
+        <f t="shared" si="0"/>
         <v>-0.41989361203460795</v>
       </c>
       <c r="Z9" s="5">
-        <f>S9-D9</f>
+        <f t="shared" si="0"/>
         <v>0.28154329504869546</v>
       </c>
       <c r="AA9" s="5">
-        <f>T9-E9</f>
+        <f t="shared" si="0"/>
         <v>8.7054997268268194E-2</v>
       </c>
       <c r="AB9" s="5">
-        <f>U9-F9</f>
+        <f t="shared" si="0"/>
         <v>-0.2473393233731489</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.28509925728453994</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.3501246740177143E-2</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.33361646770387843</v>
       </c>
       <c r="AF9" s="13"/>
@@ -2816,39 +2816,39 @@
         <v>64.880143661048137</v>
       </c>
       <c r="W10" s="5">
-        <f>P10-A10</f>
+        <f t="shared" si="0"/>
         <v>0.69881193034726818</v>
       </c>
       <c r="X10" s="5">
-        <f>Q10-B10</f>
+        <f t="shared" si="0"/>
         <v>9.9997848745198376E-2</v>
       </c>
       <c r="Y10" s="5">
-        <f>R10-C10</f>
+        <f t="shared" si="0"/>
         <v>-0.3741712667518331</v>
       </c>
       <c r="Z10" s="5">
-        <f>S10-D10</f>
+        <f t="shared" si="0"/>
         <v>0.19813104811372051</v>
       </c>
       <c r="AA10" s="5">
-        <f>T10-E10</f>
+        <f t="shared" si="0"/>
         <v>0.15999740952861821</v>
       </c>
       <c r="AB10" s="5">
-        <f>U10-F10</f>
+        <f t="shared" si="0"/>
         <v>-1.1574831444850369</v>
       </c>
       <c r="AC10" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.44847148923049435</v>
       </c>
       <c r="AD10" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12999762913690829</v>
       </c>
       <c r="AE10" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76582720561843498</v>
       </c>
     </row>
@@ -5080,12 +5080,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5342,17 +5341,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5377,18 +5386,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>